--- a/src/main/resources/SubrecipientOrganization_Field_Values.xlsx
+++ b/src/main/resources/SubrecipientOrganization_Field_Values.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C2FFBD-65B9-4969-8478-284013E9B1D0}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28FED34-4DCA-4E9A-A307-6F1A8FC04492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="60" windowWidth="20355" windowHeight="10920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
+    <sheet name="Secondary_User" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -41,19 +42,76 @@
   </si>
   <si>
     <t>LastAuditYear__c</t>
+  </si>
+  <si>
+    <t>fieldFirstName</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>Automation Runtime</t>
+  </si>
+  <si>
+    <t>fieldLastName</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>fieldPhone</t>
+  </si>
+  <si>
+    <t>fieldUserRole__c</t>
+  </si>
+  <si>
+    <t>Secondary</t>
+  </si>
+  <si>
+    <t>fieldMailingStreet</t>
+  </si>
+  <si>
+    <t>Street 1</t>
+  </si>
+  <si>
+    <t>fieldMailingCity</t>
+  </si>
+  <si>
+    <t>VA</t>
+  </si>
+  <si>
+    <t>fieldState__c</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>fieldMailingPostalCode</t>
+  </si>
+  <si>
+    <t>fieldMailingCountry</t>
+  </si>
+  <si>
+    <t>US</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1B1B1B"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -84,6 +142,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -365,13 +424,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -382,7 +441,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -393,7 +452,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -402,6 +461,130 @@
       </c>
       <c r="C3">
         <v>2018</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23A24315-6C88-4581-823B-56D3021C7588}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>9578345724</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
